--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T16:16:52+00:00</t>
+    <t>2026-06-25T13:33:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T13:33:01+00:00</t>
+    <t>2026-06-25T13:36:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T13:36:54+00:00</t>
+    <t>2026-06-26T14:17:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13948" uniqueCount="1219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13948" uniqueCount="1218">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T14:17:25+00:00</t>
+    <t>2026-06-26T14:37:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3607,10 +3607,6 @@
   </si>
   <si>
     <t>Permet de définir le mode de prise en charge</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-regle-ModePriseEnCharge:Les codes possibles pour le mode de prise en charge sont : 46 (Hébergement (accueil jour et nuit)) ; 47 (Accueil de jour); 48 (Accueil de nuit) {(value.coding.where(code='48').exists()) or (value.coding.where(code='47').exists()) or (value.coding.where(code='46').exists())}</t>
   </si>
   <si>
     <t>Task.input:modePriseCharge.id</t>
@@ -43834,7 +43830,7 @@
         <v>74</v>
       </c>
       <c r="AK372" t="s" s="2">
-        <v>1141</v>
+        <v>94</v>
       </c>
     </row>
     <row r="373">
@@ -43842,7 +43838,7 @@
         <v>839</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="C373" t="s" s="2">
         <v>1028</v>
@@ -43945,7 +43941,7 @@
         <v>839</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C374" t="s" s="2">
         <v>1029</v>
@@ -44050,7 +44046,7 @@
         <v>839</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="C375" t="s" s="2">
         <v>1030</v>
@@ -44157,7 +44153,7 @@
         <v>839</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="C376" t="s" s="2">
         <v>1031</v>
@@ -44205,7 +44201,7 @@
         <v>74</v>
       </c>
       <c r="T376" t="s" s="2">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="U376" t="s" s="2">
         <v>74</v>
@@ -44264,7 +44260,7 @@
         <v>839</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="C377" t="s" s="2">
         <v>1038</v>
@@ -44327,7 +44323,7 @@
       </c>
       <c r="Z377" s="2"/>
       <c r="AA377" t="s" s="2">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="AB377" t="s" s="2">
         <v>74</v>
@@ -44365,10 +44361,10 @@
         <v>839</v>
       </c>
       <c r="B378" t="s" s="2">
+        <v>1148</v>
+      </c>
+      <c r="C378" t="s" s="2">
         <v>1149</v>
-      </c>
-      <c r="C378" t="s" s="2">
-        <v>1150</v>
       </c>
       <c r="D378" s="2"/>
       <c r="E378" t="s" s="2">
@@ -44468,10 +44464,10 @@
         <v>839</v>
       </c>
       <c r="B379" t="s" s="2">
+        <v>1150</v>
+      </c>
+      <c r="C379" t="s" s="2">
         <v>1151</v>
-      </c>
-      <c r="C379" t="s" s="2">
-        <v>1152</v>
       </c>
       <c r="D379" s="2"/>
       <c r="E379" t="s" s="2">
@@ -44573,10 +44569,10 @@
         <v>839</v>
       </c>
       <c r="B380" t="s" s="2">
+        <v>1152</v>
+      </c>
+      <c r="C380" t="s" s="2">
         <v>1153</v>
-      </c>
-      <c r="C380" t="s" s="2">
-        <v>1154</v>
       </c>
       <c r="D380" s="2"/>
       <c r="E380" t="s" s="2">
@@ -44680,10 +44676,10 @@
         <v>839</v>
       </c>
       <c r="B381" t="s" s="2">
+        <v>1154</v>
+      </c>
+      <c r="C381" t="s" s="2">
         <v>1155</v>
-      </c>
-      <c r="C381" t="s" s="2">
-        <v>1156</v>
       </c>
       <c r="D381" s="2"/>
       <c r="E381" t="s" s="2">
@@ -44787,13 +44783,13 @@
         <v>839</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C382" t="s" s="2">
         <v>1021</v>
       </c>
       <c r="D382" t="s" s="2">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="E382" t="s" s="2">
         <v>1022</v>
@@ -44818,7 +44814,7 @@
         <v>135</v>
       </c>
       <c r="M382" t="s" s="2">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="N382" t="s" s="2">
         <v>1025</v>
@@ -44894,7 +44890,7 @@
         <v>839</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C383" t="s" s="2">
         <v>1028</v>
@@ -44997,7 +44993,7 @@
         <v>839</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="C384" t="s" s="2">
         <v>1029</v>
@@ -45102,7 +45098,7 @@
         <v>839</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="C385" t="s" s="2">
         <v>1030</v>
@@ -45209,7 +45205,7 @@
         <v>839</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="C386" t="s" s="2">
         <v>1031</v>
@@ -45257,7 +45253,7 @@
         <v>74</v>
       </c>
       <c r="T386" t="s" s="2">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="U386" t="s" s="2">
         <v>74</v>
@@ -45316,7 +45312,7 @@
         <v>839</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="C387" t="s" s="2">
         <v>1038</v>
@@ -45379,7 +45375,7 @@
       </c>
       <c r="Z387" s="2"/>
       <c r="AA387" t="s" s="2">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="AB387" t="s" s="2">
         <v>74</v>
@@ -45417,13 +45413,13 @@
         <v>839</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C388" t="s" s="2">
         <v>1021</v>
       </c>
       <c r="D388" t="s" s="2">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E388" t="s" s="2">
         <v>1022</v>
@@ -45448,7 +45444,7 @@
         <v>135</v>
       </c>
       <c r="M388" t="s" s="2">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="N388" t="s" s="2">
         <v>1025</v>
@@ -45524,7 +45520,7 @@
         <v>839</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C389" t="s" s="2">
         <v>1028</v>
@@ -45627,7 +45623,7 @@
         <v>839</v>
       </c>
       <c r="B390" t="s" s="2">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C390" t="s" s="2">
         <v>1029</v>
@@ -45732,7 +45728,7 @@
         <v>839</v>
       </c>
       <c r="B391" t="s" s="2">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C391" t="s" s="2">
         <v>1030</v>
@@ -45839,7 +45835,7 @@
         <v>839</v>
       </c>
       <c r="B392" t="s" s="2">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C392" t="s" s="2">
         <v>1031</v>
@@ -45887,7 +45883,7 @@
         <v>74</v>
       </c>
       <c r="T392" t="s" s="2">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="U392" t="s" s="2">
         <v>74</v>
@@ -45946,7 +45942,7 @@
         <v>839</v>
       </c>
       <c r="B393" t="s" s="2">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C393" t="s" s="2">
         <v>1038</v>
@@ -46049,13 +46045,13 @@
         <v>839</v>
       </c>
       <c r="B394" t="s" s="2">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C394" t="s" s="2">
         <v>1021</v>
       </c>
       <c r="D394" t="s" s="2">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="E394" t="s" s="2">
         <v>1022</v>
@@ -46080,7 +46076,7 @@
         <v>135</v>
       </c>
       <c r="M394" t="s" s="2">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="N394" t="s" s="2">
         <v>1025</v>
@@ -46156,7 +46152,7 @@
         <v>839</v>
       </c>
       <c r="B395" t="s" s="2">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C395" t="s" s="2">
         <v>1028</v>
@@ -46259,7 +46255,7 @@
         <v>839</v>
       </c>
       <c r="B396" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C396" t="s" s="2">
         <v>1029</v>
@@ -46364,7 +46360,7 @@
         <v>839</v>
       </c>
       <c r="B397" t="s" s="2">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C397" t="s" s="2">
         <v>1030</v>
@@ -46471,7 +46467,7 @@
         <v>839</v>
       </c>
       <c r="B398" t="s" s="2">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C398" t="s" s="2">
         <v>1031</v>
@@ -46519,7 +46515,7 @@
         <v>74</v>
       </c>
       <c r="T398" t="s" s="2">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="U398" t="s" s="2">
         <v>74</v>
@@ -46578,7 +46574,7 @@
         <v>839</v>
       </c>
       <c r="B399" t="s" s="2">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C399" t="s" s="2">
         <v>1038</v>
@@ -46607,7 +46603,7 @@
         <v>357</v>
       </c>
       <c r="M399" t="s" s="2">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="N399" t="s" s="2">
         <v>1041</v>
@@ -46641,7 +46637,7 @@
       </c>
       <c r="Z399" s="2"/>
       <c r="AA399" t="s" s="2">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="AB399" t="s" s="2">
         <v>74</v>
@@ -46679,7 +46675,7 @@
         <v>839</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C400" t="s" s="2">
         <v>1021</v>
@@ -46710,7 +46706,7 @@
         <v>135</v>
       </c>
       <c r="M400" t="s" s="2">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="N400" t="s" s="2">
         <v>1025</v>
@@ -46786,7 +46782,7 @@
         <v>839</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C401" t="s" s="2">
         <v>1028</v>
@@ -46889,7 +46885,7 @@
         <v>839</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C402" t="s" s="2">
         <v>1029</v>
@@ -46994,7 +46990,7 @@
         <v>839</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C403" t="s" s="2">
         <v>1030</v>
@@ -47101,7 +47097,7 @@
         <v>839</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C404" t="s" s="2">
         <v>1031</v>
@@ -47149,7 +47145,7 @@
         <v>74</v>
       </c>
       <c r="T404" t="s" s="2">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="U404" t="s" s="2">
         <v>74</v>
@@ -47208,7 +47204,7 @@
         <v>839</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C405" t="s" s="2">
         <v>1038</v>
@@ -47311,7 +47307,7 @@
         <v>839</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C406" t="s" s="2">
         <v>1021</v>
@@ -47342,7 +47338,7 @@
         <v>135</v>
       </c>
       <c r="M406" t="s" s="2">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="N406" t="s" s="2">
         <v>1025</v>
@@ -47418,7 +47414,7 @@
         <v>839</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="C407" t="s" s="2">
         <v>1028</v>
@@ -47521,7 +47517,7 @@
         <v>839</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C408" t="s" s="2">
         <v>1029</v>
@@ -47626,7 +47622,7 @@
         <v>839</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C409" t="s" s="2">
         <v>1030</v>
@@ -47733,7 +47729,7 @@
         <v>839</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="C410" t="s" s="2">
         <v>1031</v>
@@ -47781,7 +47777,7 @@
         <v>74</v>
       </c>
       <c r="T410" t="s" s="2">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="U410" t="s" s="2">
         <v>74</v>
@@ -47840,7 +47836,7 @@
         <v>839</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C411" t="s" s="2">
         <v>1038</v>
@@ -47943,10 +47939,10 @@
         <v>839</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="D412" s="2"/>
       <c r="E412" t="s" s="2">
@@ -47972,14 +47968,14 @@
         <v>135</v>
       </c>
       <c r="M412" t="s" s="2">
+        <v>1203</v>
+      </c>
+      <c r="N412" t="s" s="2">
         <v>1204</v>
-      </c>
-      <c r="N412" t="s" s="2">
-        <v>1205</v>
       </c>
       <c r="O412" s="2"/>
       <c r="P412" t="s" s="2">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="Q412" t="s" s="2">
         <v>74</v>
@@ -48028,7 +48024,7 @@
         <v>74</v>
       </c>
       <c r="AG412" t="s" s="2">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="AH412" t="s" s="2">
         <v>75</v>
@@ -48048,10 +48044,10 @@
         <v>839</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="D413" s="2"/>
       <c r="E413" t="s" s="2">
@@ -48151,10 +48147,10 @@
         <v>839</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D414" s="2"/>
       <c r="E414" t="s" s="2">
@@ -48256,10 +48252,10 @@
         <v>839</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D415" s="2"/>
       <c r="E415" t="s" s="2">
@@ -48363,10 +48359,10 @@
         <v>839</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D416" s="2"/>
       <c r="E416" t="s" s="2">
@@ -48392,14 +48388,14 @@
         <v>357</v>
       </c>
       <c r="M416" t="s" s="2">
+        <v>1210</v>
+      </c>
+      <c r="N416" t="s" s="2">
         <v>1211</v>
-      </c>
-      <c r="N416" t="s" s="2">
-        <v>1212</v>
       </c>
       <c r="O416" s="2"/>
       <c r="P416" t="s" s="2">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="Q416" t="s" s="2">
         <v>74</v>
@@ -48427,7 +48423,7 @@
         <v>318</v>
       </c>
       <c r="Z416" t="s" s="2">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="AA416" t="s" s="2">
         <v>74</v>
@@ -48448,7 +48444,7 @@
         <v>74</v>
       </c>
       <c r="AG416" t="s" s="2">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="AH416" t="s" s="2">
         <v>82</v>
@@ -48468,10 +48464,10 @@
         <v>839</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="D417" s="2"/>
       <c r="E417" t="s" s="2">
@@ -48497,14 +48493,14 @@
         <v>1039</v>
       </c>
       <c r="M417" t="s" s="2">
+        <v>1215</v>
+      </c>
+      <c r="N417" t="s" s="2">
         <v>1216</v>
-      </c>
-      <c r="N417" t="s" s="2">
-        <v>1217</v>
       </c>
       <c r="O417" s="2"/>
       <c r="P417" t="s" s="2">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="Q417" t="s" s="2">
         <v>74</v>
@@ -48553,7 +48549,7 @@
         <v>74</v>
       </c>
       <c r="AG417" t="s" s="2">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="AH417" t="s" s="2">
         <v>82</v>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.0.6</t>
+    <t>4.0.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T14:37:44+00:00</t>
+    <t>2026-06-29T07:12:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T07:12:03+00:00</t>
+    <t>2026-06-29T08:05:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T08:05:43+00:00</t>
+    <t>2026-06-29T08:06:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T08:06:46+00:00</t>
+    <t>2026-06-29T08:11:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T08:11:30+00:00</t>
+    <t>2026-06-29T08:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T08:20:47+00:00</t>
+    <t>2026-06-29T08:37:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
